--- a/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.10_b0.10_x0.10_Q10_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.10_b0.10_x0.10_Q10_LO.xlsx
@@ -455,13 +455,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.009546868444566339</v>
+        <v>0.009296896513051477</v>
       </c>
       <c r="C2" t="n">
-        <v>0.009546868444566339</v>
+        <v>0.009296896513051477</v>
       </c>
       <c r="D2" t="n">
-        <v>0.005068558686473489</v>
+        <v>0.005240342049505174</v>
       </c>
     </row>
     <row r="3">
@@ -469,13 +469,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.009473584393541588</v>
+        <v>0.009191954662659721</v>
       </c>
       <c r="C3" t="n">
-        <v>0.009473584393541588</v>
+        <v>0.009191954662659721</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004814162336414034</v>
+        <v>0.004902081080478076</v>
       </c>
     </row>
     <row r="4">
@@ -483,13 +483,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.009285534749835577</v>
+        <v>0.008963709911774221</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009285534749835577</v>
+        <v>0.008963709911774221</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004639463463926724</v>
+        <v>0.004601271827737946</v>
       </c>
     </row>
     <row r="5">
@@ -497,13 +497,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.008991781031236589</v>
+        <v>0.008630695399980787</v>
       </c>
       <c r="C5" t="n">
-        <v>0.008991781031236589</v>
+        <v>0.008630695399980787</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004481896724263275</v>
+        <v>0.004311401852437127</v>
       </c>
     </row>
     <row r="6">
@@ -511,13 +511,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.008694222418836554</v>
+        <v>0.00830326649248363</v>
       </c>
       <c r="C6" t="n">
-        <v>0.008694222418836554</v>
+        <v>0.00830326649248363</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00424501663531562</v>
+        <v>0.003994149926191649</v>
       </c>
     </row>
     <row r="7">
@@ -525,13 +525,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.008462570817190781</v>
+        <v>0.008054843581795914</v>
       </c>
       <c r="C7" t="n">
-        <v>0.008462570817190781</v>
+        <v>0.008054843581795914</v>
       </c>
       <c r="D7" t="n">
-        <v>0.003911442168580501</v>
+        <v>0.003646117413259263</v>
       </c>
     </row>
     <row r="8">
@@ -539,13 +539,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.008327850457085771</v>
+        <v>0.007915804026422345</v>
       </c>
       <c r="C8" t="n">
-        <v>0.008327850457085771</v>
+        <v>0.007915804026422345</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003496751322701837</v>
+        <v>0.003272718299339401</v>
       </c>
     </row>
     <row r="9">
@@ -553,13 +553,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.008323925728292093</v>
+        <v>0.0079177099782968</v>
       </c>
       <c r="C9" t="n">
-        <v>0.008323925728292093</v>
+        <v>0.0079177099782968</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003045046744653617</v>
+        <v>0.002897627127969291</v>
       </c>
     </row>
     <row r="10">
@@ -567,13 +567,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.008418057275958691</v>
+        <v>0.00802696298359009</v>
       </c>
       <c r="C10" t="n">
-        <v>0.008418057275958691</v>
+        <v>0.00802696298359009</v>
       </c>
       <c r="D10" t="n">
-        <v>0.002637350807152911</v>
+        <v>0.002612499488269335</v>
       </c>
     </row>
     <row r="11">
@@ -581,13 +581,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.008829575670744275</v>
+        <v>0.008454208443617625</v>
       </c>
       <c r="C11" t="n">
-        <v>0.008829575670744275</v>
+        <v>0.008454208443617625</v>
       </c>
       <c r="D11" t="n">
-        <v>0.002364273840048488</v>
+        <v>0.002460128047358285</v>
       </c>
     </row>
     <row r="12">
@@ -595,13 +595,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.009421561923683141</v>
+        <v>0.009064784125116604</v>
       </c>
       <c r="C12" t="n">
-        <v>0.009421561923683141</v>
+        <v>0.009064784125116604</v>
       </c>
       <c r="D12" t="n">
-        <v>0.00225487402267328</v>
+        <v>0.002447525129443123</v>
       </c>
     </row>
     <row r="13">
@@ -609,13 +609,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.01027460302965984</v>
+        <v>0.009935543464100796</v>
       </c>
       <c r="C13" t="n">
-        <v>0.01027460302965984</v>
+        <v>0.009935543464100796</v>
       </c>
       <c r="D13" t="n">
-        <v>0.002292485018179505</v>
+        <v>0.002529683560194681</v>
       </c>
     </row>
     <row r="14">
@@ -623,13 +623,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.01145544029791536</v>
+        <v>0.01113055555559702</v>
       </c>
       <c r="C14" t="n">
-        <v>0.01145544029791536</v>
+        <v>0.01113055555559702</v>
       </c>
       <c r="D14" t="n">
-        <v>0.002419326198801767</v>
+        <v>0.002659364408324782</v>
       </c>
     </row>
     <row r="15">
@@ -637,13 +637,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.01286115572141733</v>
+        <v>0.01254675698440664</v>
       </c>
       <c r="C15" t="n">
-        <v>0.01286115572141733</v>
+        <v>0.01254675698440664</v>
       </c>
       <c r="D15" t="n">
-        <v>0.002607440146787622</v>
+        <v>0.002819135967496334</v>
       </c>
     </row>
     <row r="16">
@@ -651,13 +651,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.01451566409917743</v>
+        <v>0.01420504836942958</v>
       </c>
       <c r="C16" t="n">
-        <v>0.01451566409917743</v>
+        <v>0.01420504836942958</v>
       </c>
       <c r="D16" t="n">
-        <v>0.002870208722212589</v>
+        <v>0.003033826617551431</v>
       </c>
     </row>
     <row r="17">
@@ -665,13 +665,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.01636309000180139</v>
+        <v>0.01604716376062276</v>
       </c>
       <c r="C17" t="n">
-        <v>0.01636309000180139</v>
+        <v>0.01604716376062276</v>
       </c>
       <c r="D17" t="n">
-        <v>0.003300841674564042</v>
+        <v>0.003419711864722005</v>
       </c>
     </row>
     <row r="18">
@@ -679,13 +679,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.01833269373854136</v>
+        <v>0.01799926017954245</v>
       </c>
       <c r="C18" t="n">
-        <v>0.01833269373854136</v>
+        <v>0.01799926017954245</v>
       </c>
       <c r="D18" t="n">
-        <v>0.004001534980486087</v>
+        <v>0.004094283950208683</v>
       </c>
     </row>
     <row r="19">
@@ -693,13 +693,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.02043380294044387</v>
+        <v>0.02006685565435586</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02043380294044387</v>
+        <v>0.02006685565435586</v>
       </c>
       <c r="D19" t="n">
-        <v>0.004920905751295447</v>
+        <v>0.004984810647134882</v>
       </c>
     </row>
     <row r="20">
@@ -707,13 +707,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.02263447180172837</v>
+        <v>0.02221638720691804</v>
       </c>
       <c r="C20" t="n">
-        <v>0.02263447180172837</v>
+        <v>0.02221638720691804</v>
       </c>
       <c r="D20" t="n">
-        <v>0.005861596161194176</v>
+        <v>0.005898298861708589</v>
       </c>
     </row>
     <row r="21">
@@ -721,13 +721,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.02482105843748871</v>
+        <v>0.02433532883925363</v>
       </c>
       <c r="C21" t="n">
-        <v>0.02482105843748871</v>
+        <v>0.02433532883925363</v>
       </c>
       <c r="D21" t="n">
-        <v>0.006543582489013683</v>
+        <v>0.00656688157628378</v>
       </c>
     </row>
     <row r="22">
@@ -735,13 +735,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0.02694317602560597</v>
+        <v>0.02637681228008717</v>
       </c>
       <c r="C22" t="n">
-        <v>0.02694317602560597</v>
+        <v>0.02637681228008717</v>
       </c>
       <c r="D22" t="n">
-        <v>0.006753739005330357</v>
+        <v>0.006748482302397605</v>
       </c>
     </row>
     <row r="23">
@@ -749,13 +749,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0.02902203684307221</v>
+        <v>0.02836720226723757</v>
       </c>
       <c r="C23" t="n">
-        <v>0.02902203684307221</v>
+        <v>0.02836720226723757</v>
       </c>
       <c r="D23" t="n">
-        <v>0.006427070409993547</v>
+        <v>0.006393343394401544</v>
       </c>
     </row>
     <row r="24">
@@ -763,13 +763,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0.031206851927268</v>
+        <v>0.03045971032601769</v>
       </c>
       <c r="C24" t="n">
-        <v>0.031206851927268</v>
+        <v>0.03045971032601769</v>
       </c>
       <c r="D24" t="n">
-        <v>0.005755763789230749</v>
+        <v>0.005674498896894016</v>
       </c>
     </row>
     <row r="25">
@@ -777,13 +777,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0.03360352064185056</v>
+        <v>0.03276781025578659</v>
       </c>
       <c r="C25" t="n">
-        <v>0.03360352064185056</v>
+        <v>0.03276781025578659</v>
       </c>
       <c r="D25" t="n">
-        <v>0.005040037114652207</v>
+        <v>0.004906356426591253</v>
       </c>
     </row>
     <row r="26">
@@ -791,13 +791,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0.03630936290772722</v>
+        <v>0.03539250361031258</v>
       </c>
       <c r="C26" t="n">
-        <v>0.03630936290772722</v>
+        <v>0.03539250361031258</v>
       </c>
       <c r="D26" t="n">
-        <v>0.004584653136258843</v>
+        <v>0.004396925283327204</v>
       </c>
     </row>
     <row r="27">
@@ -805,13 +805,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0.03925390302114034</v>
+        <v>0.03826541414403589</v>
       </c>
       <c r="C27" t="n">
-        <v>0.03925390302114034</v>
+        <v>0.03826541414403589</v>
       </c>
       <c r="D27" t="n">
-        <v>0.004563194360256599</v>
+        <v>0.004319870908573811</v>
       </c>
     </row>
     <row r="28">
@@ -819,13 +819,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0.04240378521889218</v>
+        <v>0.04135636002249473</v>
       </c>
       <c r="C28" t="n">
-        <v>0.04240378521889218</v>
+        <v>0.04135636002249473</v>
       </c>
       <c r="D28" t="n">
-        <v>0.004896160241114891</v>
+        <v>0.004615107091330104</v>
       </c>
     </row>
     <row r="29">
@@ -833,13 +833,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.04563304431461248</v>
+        <v>0.0445380008748795</v>
       </c>
       <c r="C29" t="n">
-        <v>0.04563304431461248</v>
+        <v>0.0445380008748795</v>
       </c>
       <c r="D29" t="n">
-        <v>0.005396552439849107</v>
+        <v>0.005082607741747021</v>
       </c>
     </row>
     <row r="30">
@@ -847,13 +847,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0.04880151230769316</v>
+        <v>0.0476675542354087</v>
       </c>
       <c r="C30" t="n">
-        <v>0.04880151230769316</v>
+        <v>0.0476675542354087</v>
       </c>
       <c r="D30" t="n">
-        <v>0.005913262082259205</v>
+        <v>0.005565973687193037</v>
       </c>
     </row>
     <row r="31">
@@ -861,13 +861,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0.05183837720635096</v>
+        <v>0.0506722934728579</v>
       </c>
       <c r="C31" t="n">
-        <v>0.05183837720635096</v>
+        <v>0.0506722934728579</v>
       </c>
       <c r="D31" t="n">
-        <v>0.006397278810199085</v>
+        <v>0.006001797135027528</v>
       </c>
     </row>
   </sheetData>
